--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.9598963248689</v>
+        <v>6.980983152791197</v>
       </c>
       <c r="D2" t="n">
-        <v>40.58043165862264</v>
+        <v>6.594320144526178</v>
       </c>
       <c r="E2" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F2" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.93339542242221</v>
+        <v>6.001676756143609</v>
       </c>
       <c r="D3" t="n">
-        <v>36.09721522144196</v>
+        <v>5.865797473484319</v>
       </c>
       <c r="E3" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F3" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.80895824885628</v>
+        <v>5.006455715439146</v>
       </c>
       <c r="D4" t="n">
-        <v>21.50581316760657</v>
+        <v>3.494694639736068</v>
       </c>
       <c r="E4" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F4" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.32548452330351</v>
+        <v>2.00289123503682</v>
       </c>
       <c r="D5" t="n">
-        <v>43.88970337483563</v>
+        <v>7.13207679841079</v>
       </c>
       <c r="E5" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F5" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.04101995264802</v>
+        <v>5.206665742305304</v>
       </c>
       <c r="D6" t="n">
-        <v>33.08365341558837</v>
+        <v>5.376093680033111</v>
       </c>
       <c r="E6" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F6" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.81889794247727</v>
+        <v>6.633070915652556</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45963520530358</v>
+        <v>5.762190720861832</v>
       </c>
       <c r="E7" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F7" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.540695149743504</v>
+        <v>0.7378629618333195</v>
       </c>
       <c r="D8" t="n">
-        <v>10.711747586234</v>
+        <v>1.740658982763025</v>
       </c>
       <c r="E8" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F8" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.71864765936714</v>
+        <v>5.641780244647161</v>
       </c>
       <c r="D9" t="n">
-        <v>28.68800784030254</v>
+        <v>4.661801274049163</v>
       </c>
       <c r="E9" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F9" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.33179000486695</v>
+        <v>7.04141587579088</v>
       </c>
       <c r="D10" t="n">
-        <v>39.50708133916341</v>
+        <v>6.419900717614054</v>
       </c>
       <c r="E10" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F10" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.64228151995579</v>
+        <v>5.304370746992816</v>
       </c>
       <c r="D11" t="n">
-        <v>29.80946642713278</v>
+        <v>4.844038294409077</v>
       </c>
       <c r="E11" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F11" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.14494286162579</v>
+        <v>4.736053215014191</v>
       </c>
       <c r="D12" t="n">
-        <v>30.39123738643173</v>
+        <v>4.938576075295155</v>
       </c>
       <c r="E12" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F12" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>43.80633459354675</v>
+        <v>7.118529371451348</v>
       </c>
       <c r="D13" t="n">
-        <v>24.77032042546781</v>
+        <v>4.02517706913852</v>
       </c>
       <c r="E13" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F13" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>27.83651756092731</v>
+        <v>4.523434103650688</v>
       </c>
       <c r="D14" t="n">
-        <v>29.48457961888996</v>
+        <v>4.791244188069618</v>
       </c>
       <c r="E14" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F14" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>43.34311594843226</v>
+        <v>7.043256341620242</v>
       </c>
       <c r="D15" t="n">
-        <v>43.01223945474556</v>
+        <v>6.989488911396154</v>
       </c>
       <c r="E15" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F15" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>47.85200585502694</v>
+        <v>7.775950951441878</v>
       </c>
       <c r="D16" t="n">
-        <v>22.01860023661647</v>
+        <v>3.578022538450177</v>
       </c>
       <c r="E16" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F16" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>44.71699113331607</v>
+        <v>7.266511059163862</v>
       </c>
       <c r="D17" t="n">
-        <v>31.81587653986607</v>
+        <v>5.170079937728236</v>
       </c>
       <c r="E17" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F17" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>57.65050628924144</v>
+        <v>9.368207272001735</v>
       </c>
       <c r="D18" t="n">
-        <v>12.10686828693876</v>
+        <v>1.967366096627549</v>
       </c>
       <c r="E18" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F18" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>44.91478923102738</v>
+        <v>7.298653250041949</v>
       </c>
       <c r="D19" t="n">
-        <v>13.51165529504743</v>
+        <v>2.195643985445207</v>
       </c>
       <c r="E19" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F19" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>55.95586844296984</v>
+        <v>9.0928286219826</v>
       </c>
       <c r="D20" t="n">
-        <v>16.38438484353197</v>
+        <v>2.662462537073945</v>
       </c>
       <c r="E20" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F20" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>66.71175573031219</v>
+        <v>10.84066030617573</v>
       </c>
       <c r="D21" t="n">
-        <v>20.52848152260886</v>
+        <v>3.335878247423941</v>
       </c>
       <c r="E21" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F21" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>97.42138441472946</v>
+        <v>15.83097496739354</v>
       </c>
       <c r="D22" t="n">
-        <v>47.11789921858362</v>
+        <v>7.656658623019839</v>
       </c>
       <c r="E22" t="n">
-        <v>18.53589924468434</v>
+        <v>3.012083627261206</v>
       </c>
       <c r="F22" t="n">
-        <v>10.51930621725064</v>
+        <v>1.709387260303229</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
